--- a/FLORES DE ESTRADA/Julio/PRORRATEO Julio Estrada.xlsx
+++ b/FLORES DE ESTRADA/Julio/PRORRATEO Julio Estrada.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECDD4D2-AFF9-438B-B2F8-92007265401D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBA05BC-ED7C-4946-85E3-05F590C3EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -274,7 +274,7 @@
     <t>Federico</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/07  LIQUIDACION : JUNIO</t>
+    <t>EXPENSAS - VENCIMIENTO 14/08  LIQUIDACION : JULIO</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1096,7 @@
     <col min="8" max="8" width="13.7109375" style="6" customWidth="1"/>
     <col min="9" max="9" width="8.42578125" style="6" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1334,23 +1334,23 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>538512.34331379808</v>
+        <v>663787.08654741221</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>538512.34331379808</v>
+        <v>663787.08654741221</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>47389.086211614238</v>
+        <v>58413.263616172284</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>585901.42952541227</v>
+        <v>722200.35016358446</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>663787.08654741221</v>
+        <v>800086.0071855844</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1487,23 +1487,23 @@
         <v>77885.657021999999</v>
       </c>
       <c r="G15" s="62">
-        <f t="shared" ref="G15:G21" si="4">F15</f>
-        <v>77885.657021999999</v>
+        <f>F15-27230</f>
+        <v>50655.657021999999</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27230</v>
       </c>
       <c r="I15" s="8">
         <v>0</v>
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2396.2400000000002</v>
       </c>
       <c r="K15" s="44">
         <f>H15+J15+I15</f>
-        <v>0</v>
+        <v>29626.240000000002</v>
       </c>
       <c r="L15" s="5">
         <f>C7*E15/100</f>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N15" s="44">
         <f>K15+L15+M15</f>
-        <v>77885.657021999999</v>
+        <v>107511.897022</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -1535,23 +1535,26 @@
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>137015.2385984</v>
-      </c>
-      <c r="G16" s="62"/>
+        <v>229160.65879505922</v>
+      </c>
+      <c r="G16" s="62">
+        <f>F16</f>
+        <v>229160.65879505922</v>
+      </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>137015.2385984</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>12057.340996659201</v>
+        <v>0</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>149072.57959505921</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
@@ -1563,7 +1566,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>229160.65879505922</v>
+        <v>80088.079200000007</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1586,7 +1589,7 @@
         <v>98107.897020000004</v>
       </c>
       <c r="G17" s="62">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G15:G21" si="4">F17</f>
         <v>98107.897020000004</v>
       </c>
       <c r="H17" s="8">
@@ -1735,23 +1738,22 @@
         <v>-4377.2293319999881</v>
       </c>
       <c r="G20" s="62">
-        <f>F20+237000</f>
-        <v>232622.77066800001</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
-        <v>-237000</v>
+        <v>-4377.2293319999881</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>-20856.000000000004</v>
+        <v>-385.19618121599899</v>
       </c>
       <c r="K20" s="44">
         <f>H20+J20+I20</f>
-        <v>-257856</v>
+        <v>-4762.4255132159869</v>
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
@@ -1763,7 +1765,7 @@
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>-4377.2293319999881</v>
+        <v>248716.34515478404</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1827,33 +1829,28 @@
       <c r="C22" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="55" t="s">
-        <v>81</v>
-      </c>
+      <c r="D22" s="55"/>
       <c r="E22" s="1">
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
         <v>150365.36869799998</v>
       </c>
-      <c r="G22" s="62">
-        <f>F22</f>
+      <c r="G22" s="62"/>
+      <c r="H22" s="8">
+        <f t="shared" si="0"/>
         <v>150365.36869799998</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13232.152445423999</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>0</v>
+        <v>163597.52114342398</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
@@ -1865,7 +1862,7 @@
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>150365.36869799998</v>
+        <v>313962.88984142395</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1883,23 +1880,23 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>201832.34249857216</v>
+        <v>308691.5767484465</v>
       </c>
       <c r="G23" s="62"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>201832.34249857216</v>
+        <v>308691.5767484465</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>17761.246139874351</v>
+        <v>27164.858753863296</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>219593.58863844653</v>
+        <v>335856.43550230982</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
@@ -1911,7 +1908,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>308691.5767484465</v>
+        <v>424954.42361230979</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1980,23 +1977,25 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>258171.20084521864</v>
-      </c>
-      <c r="G25" s="62"/>
+        <v>369989.25462959788</v>
+      </c>
+      <c r="G25" s="62">
+        <v>57949</v>
+      </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>258171.20084521864</v>
+        <v>312040.25462959788</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>22719.065674379242</v>
+        <v>27459.542407404617</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>280890.26651959791</v>
+        <v>339499.79703700251</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
@@ -2008,7 +2007,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>369989.25462959788</v>
+        <v>428598.78514700249</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2028,23 +2027,23 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>713815.07459074154</v>
+        <v>960634.16311672679</v>
       </c>
       <c r="G26" s="62"/>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>713815.07459074154</v>
+        <v>960634.16311672679</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>62815.726563985263</v>
+        <v>84535.806354271961</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>776630.80115472677</v>
+        <v>1045169.9694709987</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
@@ -2056,7 +2055,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>960634.16311672679</v>
+        <v>1229173.3314329986</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2125,23 +2124,23 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>40421.583386528</v>
+        <v>67605.666088542464</v>
       </c>
       <c r="G28" s="62"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>40421.583386528</v>
+        <v>67605.666088542464</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>3557.0993380144641</v>
+        <v>5949.2986157917376</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>43978.682724542465</v>
+        <v>73554.964704334197</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
@@ -2153,7 +2152,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>67605.666088542464</v>
+        <v>97181.948068334197</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2171,23 +2170,23 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>40421.583386528</v>
+        <v>67605.666088542464</v>
       </c>
       <c r="G29" s="62"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>40421.583386528</v>
+        <v>67605.666088542464</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>3557.0993380144641</v>
+        <v>5949.2986157917376</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>43978.682724542465</v>
+        <v>73554.964704334197</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
@@ -2199,7 +2198,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>67605.666088542464</v>
+        <v>97181.948068334197</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2217,25 +2216,26 @@
         <v>1.18</v>
       </c>
       <c r="F30" s="5">
-        <v>79118.78546785879</v>
+        <v>97666.237953030359</v>
       </c>
       <c r="G30" s="62">
-        <v>11068</v>
+        <f>F30</f>
+        <v>97666.237953030359</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>68050.78546785879</v>
+        <v>0</v>
       </c>
       <c r="I30" s="5">
         <v>0</v>
       </c>
       <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v>5988.4691211715744</v>
+        <v>0</v>
       </c>
       <c r="K30" s="44">
         <f t="shared" si="7"/>
-        <v>74039.254589030359</v>
+        <v>0</v>
       </c>
       <c r="L30" s="5">
         <f>C7*E30/100+1</f>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="N30" s="44">
         <f>K30+L30+M30</f>
-        <v>97666.237953030359</v>
+        <v>23626.983364</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2417,24 +2417,21 @@
       <c r="F34" s="5">
         <v>23626.983364</v>
       </c>
-      <c r="G34" s="62">
-        <f>F34</f>
+      <c r="G34" s="62"/>
+      <c r="H34" s="8">
+        <f t="shared" si="0"/>
         <v>23626.983364</v>
-      </c>
-      <c r="H34" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2079.1745360320001</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>25706.157900031998</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
@@ -2446,7 +2443,7 @@
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>23626.983364</v>
+        <v>49333.141264031998</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
@@ -2462,15 +2459,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>3162408.8873936455</v>
+        <v>3918241.045273358</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1401168.7353059999</v>
+        <v>1341031.5093240894</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>1761240.1520876456</v>
+        <v>2577209.5359492684</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2478,7 +2475,7 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>154989.13338371279</v>
+        <v>226794.43916353563</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
@@ -2491,7 +2488,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>3918241.045273358</v>
+        <v>4806015.734914802</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">

--- a/FLORES DE ESTRADA/Julio/PRORRATEO Julio Estrada.xlsx
+++ b/FLORES DE ESTRADA/Julio/PRORRATEO Julio Estrada.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBA05BC-ED7C-4946-85E3-05F590C3EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D901ADA1-E72D-4E0A-97B7-24B7F7AF6222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>EXPENSAS - VENCIMIENTO 14/08  LIQUIDACION : JULIO</t>
+  </si>
+  <si>
+    <t>LE PUSIMOS NO PAGA LAS EXTRAORDINARIAS (DE $27230) CUANDO SI LAS HABIA PAGADO</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,6 +429,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,7 +621,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -744,6 +753,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1083,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="10" hidden="1" customWidth="1"/>
@@ -1102,7 +1116,7 @@
     <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
         <v>82</v>
       </c>
@@ -1120,7 +1134,7 @@
       <c r="M1" s="68"/>
       <c r="N1" s="69"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -1130,7 +1144,7 @@
       </c>
       <c r="N2" s="12"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1156,7 @@
       <c r="J3" s="57"/>
       <c r="N3" s="12"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
@@ -1159,7 +1173,7 @@
       <c r="M4" s="65"/>
       <c r="N4" s="66"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>45</v>
       </c>
@@ -1174,7 +1188,7 @@
       </c>
       <c r="N5" s="12"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -1182,7 +1196,7 @@
       <c r="I6" s="7"/>
       <c r="N6" s="12"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="29" t="s">
         <v>56</v>
@@ -1197,7 +1211,7 @@
       <c r="I7" s="7"/>
       <c r="N7" s="12"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="29" t="s">
         <v>57</v>
@@ -1212,7 +1226,7 @@
       <c r="I8" s="7"/>
       <c r="N8" s="12"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -1228,7 +1242,7 @@
       <c r="M9" s="21"/>
       <c r="N9" s="23"/>
     </row>
-    <row r="10" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>2</v>
       </c>
@@ -1270,7 +1284,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1</v>
       </c>
@@ -1317,7 +1331,7 @@
         <v>98107.897020000004</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>2</v>
       </c>
@@ -1365,7 +1379,7 @@
         <v>800086.0071855844</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>3</v>
       </c>
@@ -1416,7 +1430,7 @@
         <v>80088.079200000007</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>4</v>
       </c>
@@ -1467,14 +1481,14 @@
         <v>98107.897020000004</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>5</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="73" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="55" t="s">
@@ -1517,8 +1531,11 @@
         <f>K15+L15+M15</f>
         <v>107511.897022</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P15" s="71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>6</v>
       </c>
@@ -1589,7 +1606,7 @@
         <v>98107.897020000004</v>
       </c>
       <c r="G17" s="62">
-        <f t="shared" ref="G15:G21" si="4">F17</f>
+        <f t="shared" ref="G17:G21" si="4">F17</f>
         <v>98107.897020000004</v>
       </c>
       <c r="H17" s="8">
